--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq3_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq3_ArchivoIntermedio.xlsx
@@ -9,6 +9,7 @@
     <x:sheet name="ArchivoIntermedio" sheetId="1" r:id="rId2"/>
     <x:sheet name="ProgramaObjeto" sheetId="2" r:id="rId3"/>
     <x:sheet name="TABBLK" sheetId="3" r:id="rId4"/>
+    <x:sheet name="TABSIM" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -87,7 +88,7 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
-    <x:t>172FFD</x:t>
+    <x:t>172012</x:t>
   </x:si>
   <x:si>
     <x:t>0003</x:t>
@@ -129,10 +130,7 @@
     <x:t>LENGTH</x:t>
   </x:si>
   <x:si>
-    <x:t>Hex inválido</x:t>
-  </x:si>
-  <x:si>
-    <x:t>036FFF</x:t>
+    <x:t>03200C</x:t>
   </x:si>
   <x:si>
     <x:t>USE</x:t>
@@ -228,7 +226,7 @@
     <x:t>LDT</x:t>
   </x:si>
   <x:si>
-    <x:t>776FFF</x:t>
+    <x:t>772003</x:t>
   </x:si>
   <x:si>
     <x:t>0015</x:t>
@@ -240,10 +238,10 @@
     <x:t>HCOPY  000000000015</x:t>
   </x:si>
   <x:si>
-    <x:t>T0000000C172FFD4B2006290000036FFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000C0AB41075101000F1776FFF</x:t>
+    <x:t>T0000000C1720124B200629000003200C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000C0AB41075101000F1772003</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">M00000F05+COPY  </x:t>
@@ -271,6 +269,33 @@
   </x:si>
   <x:si>
     <x:t>001C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Simbolo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direccion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Relativo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bloque</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -810,10 +835,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
@@ -830,10 +855,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>14</x:v>
@@ -862,10 +887,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>14</x:v>
@@ -894,10 +919,10 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>14</x:v>
@@ -926,10 +951,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>14</x:v>
@@ -955,13 +980,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="s">
+      <x:c r="F11" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>14</x:v>
@@ -984,16 +1009,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D12" s="0" t="s">
+      <x:c r="E12" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="s">
+      <x:c r="F12" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>14</x:v>
@@ -1016,16 +1041,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>14</x:v>
@@ -1048,13 +1073,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>16</x:v>
@@ -1080,28 +1105,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F15" s="0" t="s">
+      <x:c r="G15" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G15" s="0" t="s">
+      <x:c r="H15" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H15" s="0" t="s">
+      <x:c r="I15" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
@@ -1112,19 +1137,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
+      <x:c r="F16" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F16" s="0" t="s">
+      <x:c r="G16" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
         <x:v>32</x:v>
@@ -1133,7 +1158,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
@@ -1150,10 +1175,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>40</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
         <x:v>14</x:v>
@@ -1179,13 +1204,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E18" s="0" t="s">
+      <x:c r="F18" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
         <x:v>14</x:v>
@@ -1197,7 +1222,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J18" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
@@ -1208,13 +1233,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>16</x:v>
@@ -1240,13 +1265,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
         <x:v>36</x:v>
@@ -1258,10 +1283,10 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="I20" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1272,13 +1297,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="D21" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E21" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>18</x:v>
@@ -1313,32 +1338,32 @@
   <x:dimension ref="A1:A5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="36.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="36.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1365,16 +1390,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="C1" s="0" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="D1" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="D1" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1382,10 +1407,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1396,13 +1421,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -1410,13 +1435,207 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E10"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.853482" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="B6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>84</x:v>
+      <x:c r="B7" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="A8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq3_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq3_ArchivoIntermedio.xlsx
@@ -205,7 +205,7 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>75101000*</x:t>
+    <x:t>75101000</x:t>
   </x:si>
   <x:si>
     <x:t>INPUT</x:t>
@@ -235,16 +235,19 @@
     <x:t>END</x:t>
   </x:si>
   <x:si>
-    <x:t>HCOPY  000000000015</x:t>
+    <x:t>HCOPY  00000000101C</x:t>
   </x:si>
   <x:si>
     <x:t>T0000000C1720124B200629000003200C</x:t>
   </x:si>
   <x:si>
-    <x:t>T00000C0AB41075101000F1772003</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">M00000F05+COPY  </x:t>
+    <x:t>T00000C06B41075101000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00001B01F1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00001203772003</x:t>
   </x:si>
   <x:si>
     <x:t>E000000</x:t>
@@ -1335,7 +1338,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A5"/>
+  <x:dimension ref="A1:A6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="36.139196" style="0" customWidth="1"/>
@@ -1364,6 +1367,11 @@
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
         <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:1">
+      <x:c r="A6" s="0" t="s">
+        <x:v>77</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1390,16 +1398,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1407,7 +1415,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>70</x:v>
@@ -1424,7 +1432,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>70</x:v>
@@ -1441,7 +1449,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1470,19 +1478,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -1493,13 +1501,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1510,13 +1518,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -1527,10 +1535,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>39</x:v>
@@ -1544,10 +1552,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>39</x:v>
@@ -1561,10 +1569,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>42</x:v>
@@ -1578,10 +1586,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>42</x:v>
@@ -1595,10 +1603,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>42</x:v>
@@ -1612,13 +1620,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
@@ -1629,10 +1637,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>39</x:v>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq3_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq3_ArchivoIntermedio.xlsx
@@ -8,8 +8,8 @@
   <x:sheets>
     <x:sheet name="ArchivoIntermedio" sheetId="1" r:id="rId2"/>
     <x:sheet name="ProgramaObjeto" sheetId="2" r:id="rId3"/>
-    <x:sheet name="TABBLK" sheetId="3" r:id="rId4"/>
-    <x:sheet name="TABSIM" sheetId="4" r:id="rId5"/>
+    <x:sheet name="TABSIM_DEFAULT" sheetId="3" r:id="rId4"/>
+    <x:sheet name="TABBLK_DEFAULT" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -253,6 +253,33 @@
     <x:t>E000000</x:t>
   </x:si>
   <x:si>
+    <x:t>Simbolo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direccion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NumBloq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SimboloExterno</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFAULT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
     <x:t>No. Bloque</x:t>
   </x:si>
   <x:si>
@@ -265,40 +292,10 @@
     <x:t>Dir Inicial</x:t>
   </x:si>
   <x:si>
-    <x:t>DEFAULT</x:t>
-  </x:si>
-  <x:si>
     <x:t>0007</x:t>
   </x:si>
   <x:si>
     <x:t>001C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Simbolo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Direccion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tipo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Relativo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bloque</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sí</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -651,6 +648,18 @@
   </x:sheetPr>
   <x:dimension ref="A1:J21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.282054" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.710625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="7.424911" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.282054" style="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10">
       <x:c r="A1" s="0" t="s">
@@ -1388,15 +1397,17 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D4"/>
+  <x:dimension ref="A1:E10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="3" width="8.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
@@ -1409,47 +1420,161 @@
       <x:c r="D1" s="0" t="s">
         <x:v>81</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0">
-        <x:v>0</x:v>
+      <x:c r="E1" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0">
-        <x:v>1</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>83</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0">
-        <x:v>2</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="E6" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="C7" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="A8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
         <x:v>84</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1466,184 +1591,68 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E10"/>
+  <x:dimension ref="A1:D4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.853482" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="2" max="3" width="8.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5">
+    <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
+    </x:row>
+    <x:row r="3" spans="1:4">
+      <x:c r="A3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="0">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="A6" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:5">
-      <x:c r="A7" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
-      <x:c r="A8" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:5">
-      <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5">
-      <x:c r="A10" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
